--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Expenses" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Recipes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sales" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inventory_Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Ingredients" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Inventory_Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recipes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Products" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -661,13 +661,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Recipe_ID</t>
+          <t>Sale_ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -677,313 +677,359 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ingredient_ID</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Quantity_Required</t>
+          <t>Sale_Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sale_Time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Amount</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PROD002-REC001</t>
+          <t>SALE0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PROD002</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.018</v>
+          <t>PROD001</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>21:01:11</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PROD002-REC002</t>
+          <t>SALE0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PROD002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.15</v>
+          <t>PROD001</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>23:36:21</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PROD001-REC001</t>
+          <t>SALE0003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PROD001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.018</v>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>15:12:22</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD001-REC002</t>
+          <t>SALE0004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PROD001</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.15</v>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21:36:08</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD003-REC001</t>
+          <t>SALE0005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PROD003</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.018</v>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21:37:16</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PROD003-REC002</t>
+          <t>SALE0006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PROD003</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2</v>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21:38:12</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PROD003-REC003</t>
+          <t>SALE0007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PROD003</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ING003</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.03</v>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13:18:40</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PROD003-REC004</t>
+          <t>SALE0008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PROD003</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ING004</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.03</v>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20:14:59</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PROD004-REC001</t>
+          <t>SALE0009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PROD004</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.018</v>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20:15:15</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PROD004-REC002</t>
+          <t>SALE0010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PROD004</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.15</v>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>04:32:00</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>803.5714285714284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PROD004-REC003</t>
+          <t>SALE0011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PROD004</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ING005</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.03</v>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04:32:27</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5357.142857142857</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PROD004-REC004</t>
+          <t>SALE0012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PROD004</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ING004</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PROD005-REC001</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PROD005</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.018</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PROD005-REC002</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PROD005</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PROD005-REC003</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PROD005</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ING003</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.03</v>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>22:19:52</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>669.6428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -997,347 +1043,1149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sale_ID</t>
+          <t>Log_ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Product_ID</t>
+          <t>Ingredient_ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Change_Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sale_Date</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sale_Time</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Total_Amount</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SALE0001</t>
+          <t>LOG000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PROD001</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.05399999999999999</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>21:01:11</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1500</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Product PROD001 x3</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SALE0002</t>
+          <t>LOG000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PROD001</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23:36:21</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1000</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Product PROD001 x3</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SALE0003</t>
+          <t>LOG000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PROD003</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.036</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15:12:22</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2400</v>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Product PROD001 x2</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SALE0004</t>
+          <t>LOG000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PROD004</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21:36:08</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>900</v>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Product PROD001 x2</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SALE0005</t>
+          <t>LOG000005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PROD004</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21:37:16</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1200</v>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Product PROD003 x4</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SALE0006</t>
+          <t>LOG000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PROD004</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21:38:12</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>300</v>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Product PROD003 x4</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SALE0007</t>
+          <t>LOG000007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PROD002</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
+          <t>ING003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13:18:40</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>900</v>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Product PROD003 x4</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SALE0008</t>
+          <t>LOG000008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PROD002</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
+          <t>ING004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.12</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20:14:59</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>150</v>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Product PROD003 x4</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SALE0009</t>
+          <t>LOG000009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PROD002</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>STOCK_ADD</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20:15:15</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>150</v>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Manual stock addition</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SALE0010</t>
+          <t>LOG000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PROD002</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>STOCK_ADD</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:32:00</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>803.5714285714284</v>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Manual stock addition</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SALE0011</t>
+          <t>LOG000011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PROD003</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+          <t>ING003</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>STOCK_ADD</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Manual stock addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LOG000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ING004</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>STOCK_ADD</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Manual stock addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LOG000013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ING005</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>STOCK_ADD</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Manual stock addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LOG000014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Product PROD004 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LOG000015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Product PROD004 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LOG000016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ING005</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Product PROD004 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LOG000017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ING004</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Product PROD004 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LOG000018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Product PROD004 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LOG000019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Product PROD004 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOG000020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ING005</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Product PROD004 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LOG000021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ING004</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Product PROD004 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LOG000022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.108</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Product PROD002 x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LOG000023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Product PROD002 x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LOG000024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Product PROD002 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LOG000025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Product PROD002 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LOG000026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Product PROD002 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LOG000027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Product PROD002 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LOG000028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.108</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Product PROD002 x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LOG000029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Product PROD002 x6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LOG000030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Product PROD003 x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LOG000031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Product PROD003 x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LOG000032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ING003</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Product PROD003 x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LOG000033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ING004</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Product PROD003 x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LOG000034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STOCK_ADD</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>04:32:27</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>5357.142857142857</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stock update (Operation: add, Amount: 10.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LOG000035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ING001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Product PROD002 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LOG000036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ING002</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SALE_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Product PROD002 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LOG000037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ING007</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>STOCK_ADD</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stock update (Operation: add, Amount: 15.0)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +2199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,7 +2291,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20.316</v>
+        <v>20.226</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -1482,7 +2330,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24.6</v>
+        <v>23.85</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -1669,6 +2517,129 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>2025-12-15 04:08:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ING007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Flour</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" t="n">
+        <v>220</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:22:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ING008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tomato Sauce</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Liquids</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>225</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:26:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ING009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cheese</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>650</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:26:36</t>
         </is>
       </c>
     </row>
@@ -1683,1059 +2654,389 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Log_ID</t>
+          <t>Recipe_ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Product_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Ingredient_ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Change_Type</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Quantity_Required</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LOG000001</t>
+          <t>PROD002-REC001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>ING001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D2" t="n">
-        <v>-0.05399999999999999</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Product PROD001 x3</t>
-        </is>
+        <v>0.018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LOG000002</t>
+          <t>PROD002-REC002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>PROD002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>ING002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D3" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Product PROD001 x3</t>
-        </is>
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOG000003</t>
+          <t>PROD001-REC001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PROD001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>ING001</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D4" t="n">
-        <v>-0.036</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Product PROD001 x2</t>
-        </is>
+        <v>0.018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOG000004</t>
+          <t>PROD001-REC002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>PROD001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>ING002</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Product PROD001 x2</t>
-        </is>
+        <v>0.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LOG000005</t>
+          <t>PROD003-REC001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>ING001</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D6" t="n">
-        <v>-0.07199999999999999</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Product PROD003 x4</t>
-        </is>
+        <v>0.018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LOG000006</t>
+          <t>PROD003-REC002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>ING002</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D7" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Product PROD003 x4</t>
-        </is>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOG000007</t>
+          <t>PROD003-REC003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>ING003</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D8" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Product PROD003 x4</t>
-        </is>
+        <v>0.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOG000008</t>
+          <t>PROD003-REC004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>PROD003</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>ING004</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
       <c r="D9" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Product PROD003 x4</t>
-        </is>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOG000009</t>
+          <t>PROD004-REC001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>ING001</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>STOCK_ADD</t>
-        </is>
-      </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Manual stock addition</t>
-        </is>
+        <v>0.018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOG000010</t>
+          <t>PROD004-REC002</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>ING002</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>STOCK_ADD</t>
-        </is>
-      </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Manual stock addition</t>
-        </is>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LOG000011</t>
+          <t>PROD004-REC003</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ING003</t>
+          <t>PROD004</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STOCK_ADD</t>
+          <t>ING005</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Manual stock addition</t>
-        </is>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LOG000012</t>
+          <t>PROD004-REC004</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>PROD004</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>ING004</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>STOCK_ADD</t>
-        </is>
-      </c>
       <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Manual stock addition</t>
-        </is>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LOG000013</t>
+          <t>PROD005-REC001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ING005</t>
+          <t>PROD005</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STOCK_ADD</t>
+          <t>ING001</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Manual stock addition</t>
-        </is>
+        <v>0.018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LOG000014</t>
+          <t>PROD005-REC002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ING001</t>
+          <t>PROD005</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SALE_DEDUCTION</t>
+          <t>ING002</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07199999999999999</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Product PROD004 x4</t>
-        </is>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOG000015</t>
+          <t>PROD005-REC003</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ING002</t>
+          <t>PROD005</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SALE_DEDUCTION</t>
+          <t>ING003</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Product PROD004 x4</t>
-        </is>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOG000016</t>
+          <t>PROD006-REC001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ING005</t>
+          <t>PROD006</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SALE_DEDUCTION</t>
+          <t>ING007</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Product PROD004 x4</t>
-        </is>
+        <v>0.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LOG000017</t>
+          <t>PROD006-REC002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ING004</t>
+          <t>PROD006</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SALE_DEDUCTION</t>
+          <t>ING008</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Product PROD004 x4</t>
-        </is>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LOG000018</t>
+          <t>PROD006-REC003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ING001</t>
+          <t>PROD006</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SALE_DEDUCTION</t>
+          <t>ING009</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Product PROD004 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LOG000019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Product PROD004 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LOG000020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ING005</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Product PROD004 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LOG000021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ING004</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Product PROD004 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LOG000022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>-0.108</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Product PROD002 x6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LOG000023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Product PROD002 x6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LOG000024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Product PROD002 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LOG000025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Product PROD002 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LOG000026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Product PROD002 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LOG000027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Product PROD002 x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LOG000028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>-0.108</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Product PROD002 x6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LOG000029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Product PROD002 x6</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LOG000030</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ING001</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Product PROD003 x10</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LOG000031</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Product PROD003 x10</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LOG000032</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ING003</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Product PROD003 x10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LOG000033</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ING004</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SALE_DEDUCTION</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Product PROD003 x10</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LOG000034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ING002</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>STOCK_ADD</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Stock update (Operation: add, Amount: 10.0)</t>
-        </is>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -2749,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2994,6 +3295,45 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PROD006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>69</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.049999999999997</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
